--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2018_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2018_magallanes.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 13:49</t>
+    <t xml:space="preserve">2026-09-24 00:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -669,13 +669,13 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.26</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0.13</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>-0.31</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="9">
@@ -692,13 +692,13 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.12</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0.15</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="10">
@@ -715,13 +715,13 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.17</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0.04</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="11">
@@ -738,13 +738,13 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-0.07</v>
+        <v>-0.06</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="12">
@@ -921,13 +921,13 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.27</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>0.12</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>-0.31</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="21">
@@ -944,13 +944,13 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.12</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="22">
@@ -967,13 +967,13 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>0.03</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="23">
@@ -990,13 +990,13 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.07</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="24">
@@ -1173,13 +1173,13 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>-0.76</v>
+        <v>-0.29</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>0.2</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>-0.96</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="33">
@@ -1196,13 +1196,13 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>-0.56</v>
+        <v>-0.29</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>-0.58</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="34">
@@ -1219,13 +1219,13 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="35">
@@ -1242,13 +1242,13 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>0.64</v>
+        <v>0.36</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0.51</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="36">
@@ -1425,13 +1425,13 @@
         <v>18</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>-0.71</v>
+        <v>-0.28</v>
       </c>
       <c r="F44" s="2" t="n">
         <v>0.24</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>-0.95</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="45">
@@ -1448,13 +1448,13 @@
         <v>18</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>-0.72</v>
+        <v>-0.43</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>-0.84</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="46">
@@ -1471,13 +1471,13 @@
         <v>18</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="47">
@@ -1494,13 +1494,13 @@
         <v>18</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>0.83</v>
+        <v>0.53</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>0.78</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="48">
@@ -1703,7 +1703,7 @@
         <v>0.76</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
       <c r="G57" s="2" t="n">
         <v>0.94</v>
@@ -1746,13 +1746,13 @@
         <v>18</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>-0.88</v>
+        <v>-0.84</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>-1.11</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="60">
@@ -1978,7 +1978,7 @@
         <v>-0.44</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="G70" s="2" t="n">
         <v>-0.43</v>
@@ -1998,13 +1998,13 @@
         <v>18</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>-0.71</v>
+        <v>-0.68</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>-0.7</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="72">
@@ -2181,13 +2181,13 @@
         <v>18</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.18</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.3</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>0.23</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="81">
@@ -2204,13 +2204,13 @@
         <v>18</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.32</v>
       </c>
       <c r="F81" s="2" t="n">
         <v>-0.38</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>0.12</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="82">
@@ -2227,13 +2227,13 @@
         <v>18</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>0.35</v>
+        <v>0.27</v>
       </c>
       <c r="F82" s="2" t="n">
         <v>-0.04</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>0.39</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="83">
@@ -2250,13 +2250,13 @@
         <v>18</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="F83" s="2" t="n">
         <v>0.15</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="84">
@@ -2433,13 +2433,13 @@
         <v>18</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.3</v>
       </c>
       <c r="F92" s="2" t="n">
         <v>-0.38</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="93">
@@ -2456,13 +2456,13 @@
         <v>18</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.2</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.27</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>0.1</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="94">
@@ -2479,13 +2479,13 @@
         <v>18</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>-0.09</v>
+        <v>-0.1</v>
       </c>
       <c r="F94" s="2" t="n">
         <v>-0.21</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="95">
@@ -2502,13 +2502,13 @@
         <v>18</v>
       </c>
       <c r="E95" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G95" s="2" t="n">
         <v>0.3</v>
-      </c>
-      <c r="F95" s="2" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="G95" s="2" t="n">
-        <v>0.31</v>
       </c>
     </row>
     <row r="96">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2018_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2018_magallanes.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:40</t>
+    <t xml:space="preserve">2026-10-01 23:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2018_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2018_magallanes.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:14</t>
+    <t xml:space="preserve">2026-10-05 19:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
